--- a/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_duirnal_temp_range.xlsx
+++ b/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_duirnal_temp_range.xlsx
@@ -26,24 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FF9933"/>
-        <bgColor rgb="00FF9933"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0075696F"/>
-        <bgColor rgb="0075696F"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -61,6 +49,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
         <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0075696F"/>
+        <bgColor rgb="0075696F"/>
       </patternFill>
     </fill>
     <fill>
@@ -137,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -152,31 +146,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -795,16 +777,16 @@
       <c r="C4" s="3" t="n">
         <v>43.7</v>
       </c>
-      <c r="D4" s="10" t="n">
+      <c r="D4" s="8" t="n">
         <v>31.2</v>
       </c>
-      <c r="E4" s="10" t="n">
+      <c r="E4" s="8" t="n">
         <v>17.2</v>
       </c>
-      <c r="F4" s="10" t="n">
+      <c r="F4" s="8" t="n">
         <v>24.2</v>
       </c>
-      <c r="G4" s="10" t="n">
+      <c r="G4" s="8" t="n">
         <v>14</v>
       </c>
       <c r="H4" s="3" t="n">
@@ -819,10 +801,10 @@
       <c r="K4" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="L4" s="10" t="n">
+      <c r="L4" s="8" t="n">
         <v>17.6</v>
       </c>
-      <c r="M4" s="10" t="n">
+      <c r="M4" s="8" t="n">
         <v>16.2</v>
       </c>
       <c r="N4" s="3" t="n">
@@ -834,10 +816,10 @@
       <c r="P4" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q4" s="10" t="n">
+      <c r="Q4" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="R4" s="10" t="n">
+      <c r="R4" s="8" t="n">
         <v>24.4</v>
       </c>
       <c r="S4" s="3" t="n">
@@ -849,10 +831,10 @@
       <c r="U4" s="3" t="n">
         <v>15.4</v>
       </c>
-      <c r="V4" s="10" t="n">
+      <c r="V4" s="8" t="n">
         <v>27.7</v>
       </c>
-      <c r="W4" s="10" t="n">
+      <c r="W4" s="8" t="n">
         <v>24</v>
       </c>
       <c r="X4" s="3" t="inlineStr"/>
@@ -874,32 +856,32 @@
       <c r="C5" s="3" t="n">
         <v>62.1</v>
       </c>
-      <c r="D5" s="10" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="E5" s="10" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="F5" s="10" t="n">
+      <c r="D5" s="8" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="F5" s="8" t="n">
         <v>21.5</v>
       </c>
-      <c r="G5" s="10" t="n">
+      <c r="G5" s="8" t="n">
         <v>5.7</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>8.6</v>
+        <v>1.6</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>0.3</v>
       </c>
       <c r="J5" s="3" t="inlineStr"/>
       <c r="K5" s="3" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="L5" s="10" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="L5" s="8" t="n">
         <v>19.1</v>
       </c>
-      <c r="M5" s="10" t="n">
+      <c r="M5" s="8" t="n">
         <v>18</v>
       </c>
       <c r="N5" s="3" t="n">
@@ -911,13 +893,13 @@
       <c r="P5" s="3" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q5" s="10" t="n">
+      <c r="Q5" s="8" t="n">
         <v>20.5</v>
       </c>
-      <c r="R5" s="10" t="n">
+      <c r="R5" s="8" t="n">
         <v>19.1</v>
       </c>
-      <c r="S5" s="15" t="n">
+      <c r="S5" s="3" t="n">
         <v>21.2</v>
       </c>
       <c r="T5" s="3" t="n">
@@ -926,10 +908,10 @@
       <c r="U5" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="V5" s="10" t="n">
+      <c r="V5" s="8" t="n">
         <v>20.6</v>
       </c>
-      <c r="W5" s="10" t="n">
+      <c r="W5" s="8" t="n">
         <v>18.9</v>
       </c>
       <c r="X5" s="3" t="n">
@@ -957,16 +939,16 @@
       <c r="C6" s="3" t="n">
         <v>421.6</v>
       </c>
-      <c r="D6" s="10" t="n">
+      <c r="D6" s="8" t="n">
         <v>31.4</v>
       </c>
-      <c r="E6" s="10" t="n">
+      <c r="E6" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="F6" s="10" t="n">
+      <c r="F6" s="8" t="n">
         <v>25.6</v>
       </c>
-      <c r="G6" s="10" t="n">
+      <c r="G6" s="8" t="n">
         <v>11.6</v>
       </c>
       <c r="H6" s="3" t="n">
@@ -978,13 +960,13 @@
       <c r="J6" s="3" t="n">
         <v>3.6</v>
       </c>
-      <c r="K6" s="15" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L6" s="10" t="n">
+      <c r="K6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="8" t="n">
         <v>20.3</v>
       </c>
-      <c r="M6" s="10" t="n">
+      <c r="M6" s="8" t="n">
         <v>19</v>
       </c>
       <c r="N6" s="3" t="n">
@@ -996,10 +978,10 @@
       <c r="P6" s="3" t="n">
         <v>2.7</v>
       </c>
-      <c r="Q6" s="10" t="n">
+      <c r="Q6" s="8" t="n">
         <v>29.8</v>
       </c>
-      <c r="R6" s="10" t="n">
+      <c r="R6" s="8" t="n">
         <v>23.9</v>
       </c>
       <c r="S6" s="3" t="n">
@@ -1011,10 +993,10 @@
       <c r="U6" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="V6" s="10" t="n">
+      <c r="V6" s="8" t="n">
         <v>26.2</v>
       </c>
-      <c r="W6" s="10" t="n">
+      <c r="W6" s="8" t="n">
         <v>23.2</v>
       </c>
       <c r="X6" s="3" t="n">
@@ -1042,19 +1024,19 @@
       <c r="C7" s="3" t="n">
         <v>43.7</v>
       </c>
-      <c r="D7" s="10" t="n">
+      <c r="D7" s="8" t="n">
         <v>33</v>
       </c>
-      <c r="E7" s="10" t="n">
+      <c r="E7" s="8" t="n">
         <v>17</v>
       </c>
-      <c r="F7" s="10" t="n">
+      <c r="F7" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="G7" s="10" t="n">
+      <c r="G7" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="H7" s="15" t="n">
+      <c r="H7" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="I7" s="3" t="n">
@@ -1064,42 +1046,42 @@
         <v>4.9</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="8" t="n">
         <v>17.3</v>
       </c>
-      <c r="M7" s="10" t="n">
+      <c r="M7" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="N7" s="15" t="n">
+      <c r="N7" s="3" t="n">
         <v>17.3</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>872.6</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q7" s="10" t="n">
+      <c r="Q7" s="8" t="n">
         <v>31.9</v>
       </c>
-      <c r="R7" s="10" t="n">
+      <c r="R7" s="8" t="n">
         <v>23.9</v>
       </c>
       <c r="S7" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>152.1</v>
+        <v>52.1</v>
       </c>
       <c r="U7" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="V7" s="10" t="n">
+      <c r="V7" s="8" t="n">
         <v>27.6</v>
       </c>
-      <c r="W7" s="10" t="n">
+      <c r="W7" s="8" t="n">
         <v>24.1</v>
       </c>
       <c r="X7" s="3" t="n">
@@ -1125,18 +1107,18 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>29.7</v>
-      </c>
-      <c r="D8" s="10" t="n">
+        <v>297.2</v>
+      </c>
+      <c r="D8" s="8" t="n">
         <v>32.6</v>
       </c>
-      <c r="E8" s="10" t="n">
+      <c r="E8" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="F8" s="10" t="n">
+      <c r="F8" s="8" t="n">
         <v>26.2</v>
       </c>
-      <c r="G8" s="10" t="n">
+      <c r="G8" s="8" t="n">
         <v>12.8</v>
       </c>
       <c r="H8" s="3" t="n">
@@ -1151,10 +1133,10 @@
       <c r="K8" s="3" t="n">
         <v>18.5</v>
       </c>
-      <c r="L8" s="10" t="n">
+      <c r="L8" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="M8" s="10" t="n">
+      <c r="M8" s="8" t="n">
         <v>18.6</v>
       </c>
       <c r="N8" s="3" t="n">
@@ -1166,10 +1148,10 @@
       <c r="P8" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q8" s="10" t="n">
+      <c r="Q8" s="8" t="n">
         <v>26.6</v>
       </c>
-      <c r="R8" s="10" t="n">
+      <c r="R8" s="8" t="n">
         <v>26</v>
       </c>
       <c r="S8" s="3" t="n">
@@ -1181,17 +1163,17 @@
       <c r="U8" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="V8" s="10" t="n">
+      <c r="V8" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="W8" s="10" t="n">
+      <c r="W8" s="8" t="n">
         <v>22.8</v>
       </c>
       <c r="X8" s="3" t="n">
         <v>27.8</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>175.2</v>
+        <v>75.2</v>
       </c>
       <c r="Z8" s="3" t="n">
         <v>27</v>
@@ -1212,14 +1194,14 @@
       <c r="C9" s="3" t="n">
         <v>166.6</v>
       </c>
-      <c r="D9" s="9" t="n">
-        <v>852.6</v>
-      </c>
-      <c r="E9" s="9" t="n">
+      <c r="D9" s="8" t="n">
+        <v>152.6</v>
+      </c>
+      <c r="E9" s="8" t="n">
         <v>92.5</v>
       </c>
-      <c r="F9" s="9" t="n">
-        <v>822.5</v>
+      <c r="F9" s="8" t="n">
+        <v>122.5</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>6</v>
@@ -1233,29 +1215,29 @@
       <c r="J9" s="3" t="n">
         <v>15.5</v>
       </c>
-      <c r="K9" s="9" t="n">
+      <c r="K9" s="13" t="n">
         <v>44.2</v>
       </c>
-      <c r="L9" s="10" t="n">
+      <c r="L9" s="8" t="n">
         <v>94.3</v>
       </c>
-      <c r="M9" s="10" t="n">
+      <c r="M9" s="8" t="n">
         <v>87.8</v>
       </c>
       <c r="N9" s="3" t="n">
         <v>96.3</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>440.9</v>
+        <v>22.2</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>12.9</v>
       </c>
-      <c r="Q9" s="10" t="n">
+      <c r="Q9" s="8" t="n">
         <v>138.8</v>
       </c>
-      <c r="R9" s="9" t="n">
-        <v>1617.3</v>
+      <c r="R9" s="8" t="n">
+        <v>117.3</v>
       </c>
       <c r="S9" s="3" t="n">
         <v>131.9</v>
@@ -1266,10 +1248,10 @@
       <c r="U9" s="3" t="n">
         <v>58.5</v>
       </c>
-      <c r="V9" s="10" t="n">
+      <c r="V9" s="8" t="n">
         <v>126.1</v>
       </c>
-      <c r="W9" s="10" t="n">
+      <c r="W9" s="8" t="n">
         <v>113</v>
       </c>
       <c r="X9" s="3" t="n">
@@ -1297,16 +1279,16 @@
       <c r="C10" s="3" t="n">
         <v>33.3</v>
       </c>
-      <c r="D10" s="10" t="n">
+      <c r="D10" s="8" t="n">
         <v>30.5</v>
       </c>
-      <c r="E10" s="10" t="n">
+      <c r="E10" s="8" t="n">
         <v>18.5</v>
       </c>
-      <c r="F10" s="10" t="n">
+      <c r="F10" s="8" t="n">
         <v>24.5</v>
       </c>
-      <c r="G10" s="10" t="n">
+      <c r="G10" s="8" t="n">
         <v>12</v>
       </c>
       <c r="H10" s="3" t="n">
@@ -1321,13 +1303,13 @@
       <c r="K10" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L10" s="10" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="M10" s="9" t="n">
-        <v>87.59999999999999</v>
-      </c>
-      <c r="N10" s="15" t="n">
+      <c r="L10" s="13" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="M10" s="8" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="N10" s="3" t="n">
         <v>19.3</v>
       </c>
       <c r="O10" s="3" t="n">
@@ -1336,10 +1318,10 @@
       <c r="P10" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q10" s="10" t="n">
+      <c r="Q10" s="8" t="n">
         <v>27.8</v>
       </c>
-      <c r="R10" s="10" t="n">
+      <c r="R10" s="8" t="n">
         <v>23.5</v>
       </c>
       <c r="S10" s="3" t="n">
@@ -1351,10 +1333,10 @@
       <c r="U10" s="3" t="n">
         <v>11.7</v>
       </c>
-      <c r="V10" s="10" t="n">
+      <c r="V10" s="8" t="n">
         <v>25.2</v>
       </c>
-      <c r="W10" s="10" t="n">
+      <c r="W10" s="8" t="n">
         <v>22.6</v>
       </c>
       <c r="X10" s="3" t="n">
@@ -1382,16 +1364,16 @@
       <c r="C11" s="3" t="n">
         <v>44.5</v>
       </c>
-      <c r="D11" s="10" t="n">
+      <c r="D11" s="8" t="n">
         <v>28.7</v>
       </c>
-      <c r="E11" s="10" t="n">
+      <c r="E11" s="8" t="n">
         <v>19.9</v>
       </c>
-      <c r="F11" s="10" t="n">
+      <c r="F11" s="8" t="n">
         <v>24.3</v>
       </c>
-      <c r="G11" s="10" t="n">
+      <c r="G11" s="8" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="H11" s="3" t="n">
@@ -1406,10 +1388,10 @@
       <c r="K11" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="10" t="n">
+      <c r="L11" s="8" t="n">
         <v>20.1</v>
       </c>
-      <c r="M11" s="3" t="n">
+      <c r="M11" s="8" t="n">
         <v>18.7</v>
       </c>
       <c r="N11" s="3" t="n">
@@ -1421,14 +1403,14 @@
       <c r="P11" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q11" s="10" t="n">
+      <c r="Q11" s="8" t="n">
         <v>27.9</v>
       </c>
-      <c r="R11" s="10" t="n">
+      <c r="R11" s="8" t="n">
         <v>25.8</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>81.90000000000001</v>
+        <v>31.9</v>
       </c>
       <c r="T11" s="3" t="n">
         <v>850.1</v>
@@ -1436,10 +1418,10 @@
       <c r="U11" s="3" t="n">
         <v>5.7</v>
       </c>
-      <c r="V11" s="10" t="n">
+      <c r="V11" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="W11" s="10" t="n">
+      <c r="W11" s="8" t="n">
         <v>24.7</v>
       </c>
       <c r="X11" s="3" t="n">
@@ -1467,20 +1449,20 @@
       <c r="C12" s="3" t="n">
         <v>38.3</v>
       </c>
-      <c r="D12" s="10" t="n">
+      <c r="D12" s="8" t="n">
         <v>28.1</v>
       </c>
-      <c r="E12" s="10" t="n">
+      <c r="E12" s="8" t="n">
         <v>19.6</v>
       </c>
-      <c r="F12" s="10" t="n">
+      <c r="F12" s="8" t="n">
         <v>23.9</v>
       </c>
-      <c r="G12" s="10" t="n">
+      <c r="G12" s="8" t="n">
         <v>8.5</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>2.9</v>
@@ -1491,10 +1473,10 @@
       <c r="K12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L12" s="10" t="n">
+      <c r="L12" s="8" t="n">
         <v>20.6</v>
       </c>
-      <c r="M12" s="3" t="n">
+      <c r="M12" s="8" t="n">
         <v>19.3</v>
       </c>
       <c r="N12" s="3" t="n">
@@ -1504,12 +1486,12 @@
         <v>88.40000000000001</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="Q12" s="10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q12" s="8" t="n">
         <v>27.2</v>
       </c>
-      <c r="R12" s="10" t="n">
+      <c r="R12" s="8" t="n">
         <v>25.2</v>
       </c>
       <c r="S12" s="3" t="n">
@@ -1521,17 +1503,17 @@
       <c r="U12" s="3" t="n">
         <v>5.3</v>
       </c>
-      <c r="V12" s="10" t="n">
+      <c r="V12" s="8" t="n">
         <v>24.7</v>
       </c>
-      <c r="W12" s="10" t="n">
+      <c r="W12" s="8" t="n">
         <v>24.4</v>
       </c>
-      <c r="X12" s="15" t="n">
+      <c r="X12" s="3" t="n">
         <v>30.4</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>1197.7</v>
+        <v>97.7</v>
       </c>
       <c r="Z12" s="3" t="n">
         <v>0.7</v>
@@ -1550,18 +1532,18 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>235.6</v>
-      </c>
-      <c r="D13" s="10" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="D13" s="8" t="n">
         <v>31.1</v>
       </c>
-      <c r="E13" s="10" t="n">
+      <c r="E13" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="F13" s="10" t="n">
+      <c r="F13" s="8" t="n">
         <v>25.5</v>
       </c>
-      <c r="G13" s="10" t="n">
+      <c r="G13" s="8" t="n">
         <v>11.3</v>
       </c>
       <c r="H13" s="3" t="n">
@@ -1576,10 +1558,10 @@
       <c r="K13" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="L13" s="10" t="n">
+      <c r="L13" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="M13" s="3" t="n">
+      <c r="M13" s="8" t="n">
         <v>18.8</v>
       </c>
       <c r="N13" s="3" t="n">
@@ -1591,10 +1573,10 @@
       <c r="P13" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q13" s="10" t="n">
+      <c r="Q13" s="8" t="n">
         <v>28.6</v>
       </c>
-      <c r="R13" s="10" t="n">
+      <c r="R13" s="8" t="n">
         <v>26.3</v>
       </c>
       <c r="S13" s="3" t="n">
@@ -1606,10 +1588,10 @@
       <c r="U13" s="3" t="n">
         <v>6.4</v>
       </c>
-      <c r="V13" s="10" t="n">
+      <c r="V13" s="8" t="n">
         <v>24.7</v>
       </c>
-      <c r="W13" s="10" t="n">
+      <c r="W13" s="8" t="n">
         <v>23.8</v>
       </c>
       <c r="X13" s="3" t="n">
@@ -1635,18 +1617,18 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>37.4</v>
-      </c>
-      <c r="D14" s="10" t="n">
+        <v>374</v>
+      </c>
+      <c r="D14" s="8" t="n">
         <v>32.5</v>
       </c>
-      <c r="E14" s="10" t="n">
+      <c r="E14" s="8" t="n">
         <v>19.6</v>
       </c>
-      <c r="F14" s="10" t="n">
+      <c r="F14" s="8" t="n">
         <v>26.1</v>
       </c>
-      <c r="G14" s="10" t="n">
+      <c r="G14" s="8" t="n">
         <v>12.9</v>
       </c>
       <c r="H14" s="3" t="n">
@@ -1661,10 +1643,10 @@
       <c r="K14" s="3" t="n">
         <v>5.7</v>
       </c>
-      <c r="L14" s="10" t="n">
+      <c r="L14" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="M14" s="15" t="n">
+      <c r="M14" s="8" t="n">
         <v>18.7</v>
       </c>
       <c r="N14" s="3" t="n">
@@ -1676,10 +1658,10 @@
       <c r="P14" s="3" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q14" s="10" t="n">
+      <c r="Q14" s="8" t="n">
         <v>30.6</v>
       </c>
-      <c r="R14" s="10" t="n">
+      <c r="R14" s="8" t="n">
         <v>22.6</v>
       </c>
       <c r="S14" s="3" t="n">
@@ -1688,16 +1670,16 @@
       <c r="T14" s="3" t="n">
         <v>50.9</v>
       </c>
-      <c r="U14" s="15" t="n">
+      <c r="U14" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="V14" s="10" t="n">
+      <c r="V14" s="8" t="n">
         <v>21.9</v>
       </c>
-      <c r="W14" s="10" t="n">
+      <c r="W14" s="8" t="n">
         <v>21.1</v>
       </c>
-      <c r="X14" s="15" t="n">
+      <c r="X14" s="3" t="n">
         <v>24.5</v>
       </c>
       <c r="Y14" s="3" t="n">
@@ -1720,18 +1702,18 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>143.3</v>
-      </c>
-      <c r="D15" s="10" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="D15" s="8" t="n">
         <v>29.5</v>
       </c>
-      <c r="E15" s="10" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="F15" s="10" t="n">
+      <c r="E15" s="8" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="F15" s="8" t="n">
         <v>24.9</v>
       </c>
-      <c r="G15" s="10" t="n">
+      <c r="G15" s="8" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="H15" s="3" t="n">
@@ -1746,11 +1728,11 @@
       <c r="K15" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L15" s="10" t="n">
+      <c r="L15" s="8" t="n">
         <v>20.4</v>
       </c>
-      <c r="M15" s="15" t="n">
-        <v>29.1</v>
+      <c r="M15" s="8" t="n">
+        <v>19.1</v>
       </c>
       <c r="N15" s="3" t="n">
         <v>21.3</v>
@@ -1761,10 +1743,10 @@
       <c r="P15" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q15" s="10" t="n">
+      <c r="Q15" s="8" t="n">
         <v>28.5</v>
       </c>
-      <c r="R15" s="10" t="n">
+      <c r="R15" s="8" t="n">
         <v>23.1</v>
       </c>
       <c r="S15" s="3" t="n">
@@ -1776,13 +1758,13 @@
       <c r="U15" s="3" t="n">
         <v>14.1</v>
       </c>
-      <c r="V15" s="10" t="n">
+      <c r="V15" s="8" t="n">
         <v>24.5</v>
       </c>
-      <c r="W15" s="10" t="n">
+      <c r="W15" s="8" t="n">
         <v>21.1</v>
       </c>
-      <c r="X15" s="15" t="n">
+      <c r="X15" s="3" t="n">
         <v>22.8</v>
       </c>
       <c r="Y15" s="3" t="n">
@@ -1805,35 +1787,35 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1992.8</v>
-      </c>
-      <c r="D16" s="10" t="n">
+        <v>1992.6</v>
+      </c>
+      <c r="D16" s="8" t="n">
         <v>149.9</v>
       </c>
-      <c r="E16" s="10" t="n">
-        <v>99.5</v>
-      </c>
-      <c r="F16" s="10" t="n">
+      <c r="E16" s="8" t="n">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="F16" s="8" t="n">
         <v>124.7</v>
       </c>
-      <c r="G16" s="17" t="n">
+      <c r="G16" s="8" t="n">
         <v>50.8</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>11.1</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>115.8</v>
-      </c>
-      <c r="K16" s="16" t="inlineStr"/>
-      <c r="L16" s="9" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="K16" s="12" t="inlineStr"/>
+      <c r="L16" s="13" t="n">
         <v>1.9</v>
       </c>
-      <c r="M16" s="9" t="n">
-        <v>194.6</v>
+      <c r="M16" s="8" t="n">
+        <v>94.59999999999999</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>105.2</v>
@@ -1844,14 +1826,14 @@
       <c r="P16" s="3" t="n">
         <v>12.9</v>
       </c>
-      <c r="Q16" s="10" t="n">
+      <c r="Q16" s="8" t="n">
         <v>142.8</v>
       </c>
-      <c r="R16" s="10" t="n">
+      <c r="R16" s="8" t="n">
         <v>123</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>1042.5</v>
+        <v>142.5</v>
       </c>
       <c r="T16" s="3" t="n">
         <v>368.7</v>
@@ -1859,10 +1841,10 @@
       <c r="U16" s="3" t="n">
         <v>53.1</v>
       </c>
-      <c r="V16" s="10" t="n">
+      <c r="V16" s="8" t="n">
         <v>120.8</v>
       </c>
-      <c r="W16" s="10" t="n">
+      <c r="W16" s="8" t="n">
         <v>115.1</v>
       </c>
       <c r="X16" s="3" t="n">
@@ -1888,22 +1870,22 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>399.8</v>
-      </c>
-      <c r="D17" s="10" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="D17" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="E17" s="10" t="n">
+      <c r="E17" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="F17" s="10" t="n">
+      <c r="F17" s="8" t="n">
         <v>24.9</v>
       </c>
-      <c r="G17" s="3" t="n">
-        <v>10.6</v>
+      <c r="G17" s="8" t="n">
+        <v>10.2</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>28.1</v>
+        <v>18.1</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>2.2</v>
@@ -1911,13 +1893,13 @@
       <c r="J17" s="3" t="n">
         <v>3.2</v>
       </c>
-      <c r="K17" s="15" t="n">
-        <v>11551.5</v>
-      </c>
-      <c r="L17" s="10" t="n">
+      <c r="K17" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L17" s="8" t="n">
         <v>20.2</v>
       </c>
-      <c r="M17" s="9" t="n">
+      <c r="M17" s="8" t="n">
         <v>18.9</v>
       </c>
       <c r="N17" s="3" t="n">
@@ -1929,25 +1911,25 @@
       <c r="P17" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q17" s="10" t="n">
+      <c r="Q17" s="8" t="n">
         <v>28.6</v>
       </c>
-      <c r="R17" s="10" t="n">
+      <c r="R17" s="8" t="n">
         <v>24.6</v>
       </c>
       <c r="S17" s="3" t="n">
         <v>28.5</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>173.7</v>
+        <v>73.7</v>
       </c>
       <c r="U17" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="V17" s="10" t="n">
+      <c r="V17" s="8" t="n">
         <v>24.2</v>
       </c>
-      <c r="W17" s="10" t="n">
+      <c r="W17" s="8" t="n">
         <v>23</v>
       </c>
       <c r="X17" s="3" t="n">
@@ -1975,23 +1957,23 @@
       <c r="C18" s="3" t="n">
         <v>431.1</v>
       </c>
-      <c r="D18" s="10" t="n">
+      <c r="D18" s="8" t="n">
         <v>30.8</v>
       </c>
-      <c r="E18" s="10" t="n">
+      <c r="E18" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="F18" s="10" t="n">
+      <c r="F18" s="8" t="n">
         <v>24.9</v>
       </c>
-      <c r="G18" s="3" t="n">
-        <v>11.3</v>
+      <c r="G18" s="8" t="n">
+        <v>11.8</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>14.2</v>
+        <v>17.2</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>13.5</v>
+        <v>3.5</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>4</v>
@@ -1999,14 +1981,14 @@
       <c r="K18" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L18" s="10" t="n">
+      <c r="L18" s="8" t="n">
         <v>19.2</v>
       </c>
-      <c r="M18" s="3" t="n">
-        <v>20.8</v>
+      <c r="M18" s="8" t="n">
+        <v>17.7</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>13.3</v>
+        <v>19.3</v>
       </c>
       <c r="O18" s="3" t="n">
         <v>87</v>
@@ -2014,10 +1996,10 @@
       <c r="P18" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="Q18" s="10" t="n">
+      <c r="Q18" s="8" t="n">
         <v>28.6</v>
       </c>
-      <c r="R18" s="3" t="n">
+      <c r="R18" s="8" t="n">
         <v>23.1</v>
       </c>
       <c r="S18" s="3" t="n">
@@ -2029,11 +2011,11 @@
       <c r="U18" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="V18" s="10" t="n">
+      <c r="V18" s="8" t="n">
         <v>26</v>
       </c>
-      <c r="W18" s="10" t="n">
-        <v>25.6</v>
+      <c r="W18" s="8" t="n">
+        <v>25</v>
       </c>
       <c r="X18" s="3" t="n">
         <v>31</v>
@@ -2058,22 +2040,22 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>2223.4</v>
-      </c>
-      <c r="D19" s="10" t="n">
+        <v>423.4</v>
+      </c>
+      <c r="D19" s="8" t="n">
         <v>32.5</v>
       </c>
-      <c r="E19" s="10" t="n">
+      <c r="E19" s="8" t="n">
         <v>18.4</v>
       </c>
-      <c r="F19" s="10" t="n">
+      <c r="F19" s="8" t="n">
         <v>25.5</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>18.4</v>
+        <v>1.4</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>2.6</v>
@@ -2084,10 +2066,10 @@
       <c r="K19" s="3" t="n">
         <v>21.5</v>
       </c>
-      <c r="L19" s="10" t="n">
+      <c r="L19" s="8" t="n">
         <v>19.6</v>
       </c>
-      <c r="M19" s="15" t="n">
+      <c r="M19" s="8" t="n">
         <v>18.2</v>
       </c>
       <c r="N19" s="3" t="n">
@@ -2099,10 +2081,10 @@
       <c r="P19" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q19" s="10" t="n">
+      <c r="Q19" s="8" t="n">
         <v>31.8</v>
       </c>
-      <c r="R19" s="3" t="n">
+      <c r="R19" s="8" t="n">
         <v>24.2</v>
       </c>
       <c r="S19" s="3" t="n">
@@ -2114,10 +2096,10 @@
       <c r="U19" s="3" t="n">
         <v>21.7</v>
       </c>
-      <c r="V19" s="10" t="n">
+      <c r="V19" s="8" t="n">
         <v>25.8</v>
       </c>
-      <c r="W19" s="10" t="n">
+      <c r="W19" s="8" t="n">
         <v>23.3</v>
       </c>
       <c r="X19" s="3" t="n">
@@ -2145,34 +2127,34 @@
       <c r="C20" s="3" t="n">
         <v>25.6</v>
       </c>
-      <c r="D20" s="10" t="n">
+      <c r="D20" s="8" t="n">
         <v>27.2</v>
       </c>
-      <c r="E20" s="10" t="n">
+      <c r="E20" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="F20" s="10" t="n">
+      <c r="F20" s="8" t="n">
         <v>23.5</v>
       </c>
-      <c r="G20" s="10" t="n">
+      <c r="G20" s="8" t="n">
         <v>7.4</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>1.8</v>
+        <v>18.2</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>1.2</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="L20" s="10" t="n">
+        <v>24</v>
+      </c>
+      <c r="L20" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="M20" s="3" t="n">
+      <c r="M20" s="8" t="n">
         <v>18.8</v>
       </c>
       <c r="N20" s="3" t="n">
@@ -2184,11 +2166,11 @@
       <c r="P20" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q20" s="10" t="n">
+      <c r="Q20" s="8" t="n">
         <v>25.5</v>
       </c>
-      <c r="R20" s="17" t="n">
-        <v>24.15</v>
+      <c r="R20" s="8" t="n">
+        <v>22.15</v>
       </c>
       <c r="S20" s="3" t="n">
         <v>23.1</v>
@@ -2199,10 +2181,10 @@
       <c r="U20" s="3" t="n">
         <v>9.5</v>
       </c>
-      <c r="V20" s="10" t="n">
+      <c r="V20" s="8" t="n">
         <v>24.9</v>
       </c>
-      <c r="W20" s="10" t="n">
+      <c r="W20" s="8" t="n">
         <v>20.5</v>
       </c>
       <c r="X20" s="3" t="n">
@@ -2230,16 +2212,16 @@
       <c r="C21" s="3" t="n">
         <v>43.3</v>
       </c>
-      <c r="D21" s="10" t="n">
+      <c r="D21" s="8" t="n">
         <v>30.8</v>
       </c>
-      <c r="E21" s="10" t="n">
+      <c r="E21" s="8" t="n">
         <v>18.4</v>
       </c>
-      <c r="F21" s="10" t="n">
+      <c r="F21" s="8" t="n">
         <v>24.6</v>
       </c>
-      <c r="G21" s="10" t="n">
+      <c r="G21" s="8" t="n">
         <v>12.4</v>
       </c>
       <c r="H21" s="3" t="n">
@@ -2252,12 +2234,12 @@
         <v>3.4</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="L21" s="10" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L21" s="8" t="n">
         <v>18.8</v>
       </c>
-      <c r="M21" s="3" t="n">
+      <c r="M21" s="8" t="n">
         <v>17.3</v>
       </c>
       <c r="N21" s="3" t="n">
@@ -2269,10 +2251,10 @@
       <c r="P21" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="Q21" s="10" t="n">
+      <c r="Q21" s="8" t="n">
         <v>30.1</v>
       </c>
-      <c r="R21" s="3" t="n">
+      <c r="R21" s="8" t="n">
         <v>22.2</v>
       </c>
       <c r="S21" s="3" t="n">
@@ -2284,10 +2266,10 @@
       <c r="U21" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="V21" s="10" t="n">
+      <c r="V21" s="8" t="n">
         <v>24.3</v>
       </c>
-      <c r="W21" s="10" t="n">
+      <c r="W21" s="8" t="n">
         <v>22.4</v>
       </c>
       <c r="X21" s="3" t="n">
@@ -2297,7 +2279,7 @@
         <v>85</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>14.5</v>
+        <v>4.5</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2313,18 +2295,18 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>2374.6</v>
-      </c>
-      <c r="D22" s="10" t="n">
+        <v>374</v>
+      </c>
+      <c r="D22" s="8" t="n">
         <v>31.8</v>
       </c>
-      <c r="E22" s="10" t="n">
+      <c r="E22" s="8" t="n">
         <v>17.2</v>
       </c>
-      <c r="F22" s="10" t="n">
-        <v>24.75</v>
-      </c>
-      <c r="G22" s="10" t="n">
+      <c r="F22" s="8" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="G22" s="8" t="n">
         <v>14.6</v>
       </c>
       <c r="H22" s="3" t="n">
@@ -2339,11 +2321,11 @@
       <c r="K22" s="3" t="n">
         <v>3.7</v>
       </c>
-      <c r="L22" s="10" t="n">
+      <c r="L22" s="8" t="n">
         <v>17.6</v>
       </c>
-      <c r="M22" s="15" t="n">
-        <v>26.2</v>
+      <c r="M22" s="8" t="n">
+        <v>16.2</v>
       </c>
       <c r="N22" s="3" t="n">
         <v>17.5</v>
@@ -2354,25 +2336,25 @@
       <c r="P22" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q22" s="10" t="n">
+      <c r="Q22" s="8" t="n">
         <v>30.2</v>
       </c>
-      <c r="R22" s="3" t="n">
+      <c r="R22" s="8" t="n">
         <v>23.3</v>
       </c>
       <c r="S22" s="3" t="n">
         <v>24.2</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>256.4</v>
+        <v>56.4</v>
       </c>
       <c r="U22" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="V22" s="10" t="n">
+      <c r="V22" s="8" t="n">
         <v>21.2</v>
       </c>
-      <c r="W22" s="10" t="n">
+      <c r="W22" s="8" t="n">
         <v>19.5</v>
       </c>
       <c r="X22" s="3" t="n">
@@ -2398,36 +2380,36 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>192.5</v>
-      </c>
-      <c r="D23" s="10" t="n">
+        <v>1925.5</v>
+      </c>
+      <c r="D23" s="8" t="n">
         <v>153.1</v>
       </c>
-      <c r="E23" s="10" t="n">
+      <c r="E23" s="8" t="n">
         <v>92.8</v>
       </c>
-      <c r="F23" s="10" t="n">
+      <c r="F23" s="8" t="n">
         <v>123</v>
       </c>
-      <c r="G23" s="10" t="n">
-        <v>60.5</v>
+      <c r="G23" s="8" t="n">
+        <v>60.3</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>85.59999999999999</v>
+        <v>85</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>11.6</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="K23" s="9" t="n">
-        <v>49.5</v>
-      </c>
-      <c r="L23" s="10" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="K23" s="13" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="L23" s="8" t="n">
         <v>95.2</v>
       </c>
-      <c r="M23" s="9" t="n">
+      <c r="M23" s="8" t="n">
         <v>88.2</v>
       </c>
       <c r="N23" s="3" t="n">
@@ -2437,27 +2419,27 @@
         <v>437.2</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>113.7</v>
-      </c>
-      <c r="Q23" s="10" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="Q23" s="8" t="n">
         <v>146.2</v>
       </c>
-      <c r="R23" s="9" t="n">
+      <c r="R23" s="13" t="n">
         <v>114.3</v>
       </c>
       <c r="S23" s="3" t="n">
         <v>119</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>2895.2</v>
+        <v>295.2</v>
       </c>
       <c r="U23" s="3" t="n">
         <v>85.40000000000001</v>
       </c>
-      <c r="V23" s="10" t="n">
+      <c r="V23" s="8" t="n">
         <v>122.2</v>
       </c>
-      <c r="W23" s="9" t="n">
+      <c r="W23" s="8" t="n">
         <v>110.7</v>
       </c>
       <c r="X23" s="3" t="n">
@@ -2467,7 +2449,7 @@
         <v>411</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>0.8</v>
+        <v>27.1</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2483,22 +2465,22 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>1398.5</v>
-      </c>
-      <c r="D24" s="10" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="D24" s="8" t="n">
         <v>30.6</v>
       </c>
-      <c r="E24" s="10" t="n">
+      <c r="E24" s="8" t="n">
         <v>18.6</v>
       </c>
-      <c r="F24" s="10" t="n">
+      <c r="F24" s="8" t="n">
         <v>24.6</v>
       </c>
-      <c r="G24" s="10" t="n">
+      <c r="G24" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="H24" s="15" t="n">
-        <v>67.59999999999999</v>
+      <c r="H24" s="3" t="n">
+        <v>17.2</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>2.3</v>
@@ -2507,16 +2489,16 @@
         <v>3.1</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L24" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="M24" s="9" t="n">
+      <c r="M24" s="8" t="n">
         <v>17.6</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>12.3</v>
+        <v>19.3</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>87.40000000000001</v>
@@ -2524,10 +2506,10 @@
       <c r="P24" s="3" t="n">
         <v>2.7</v>
       </c>
-      <c r="Q24" s="10" t="n">
+      <c r="Q24" s="8" t="n">
         <v>29.2</v>
       </c>
-      <c r="R24" s="9" t="n">
+      <c r="R24" s="8" t="n">
         <v>22.9</v>
       </c>
       <c r="S24" s="3" t="n">
@@ -2537,12 +2519,12 @@
         <v>59</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="V24" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="V24" s="8" t="n">
         <v>24.4</v>
       </c>
-      <c r="W24" s="10" t="n">
+      <c r="W24" s="8" t="n">
         <v>22.1</v>
       </c>
       <c r="X24" s="3" t="n">
@@ -2568,18 +2550,18 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>2374</v>
-      </c>
-      <c r="D25" s="10" t="n">
+        <v>374</v>
+      </c>
+      <c r="D25" s="8" t="n">
         <v>32.1</v>
       </c>
-      <c r="E25" s="10" t="n">
+      <c r="E25" s="8" t="n">
         <v>19.3</v>
       </c>
-      <c r="F25" s="10" t="n">
+      <c r="F25" s="8" t="n">
         <v>25.7</v>
       </c>
-      <c r="G25" s="10" t="n">
+      <c r="G25" s="8" t="n">
         <v>12.8</v>
       </c>
       <c r="H25" s="3" t="n">
@@ -2592,12 +2574,12 @@
         <v>3.6</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="L25" s="10" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L25" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="M25" s="10" t="n">
+      <c r="M25" s="8" t="n">
         <v>18.4</v>
       </c>
       <c r="N25" s="3" t="n">
@@ -2607,16 +2589,16 @@
         <v>90</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="Q25" s="10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q25" s="8" t="n">
         <v>31.3</v>
       </c>
-      <c r="R25" s="10" t="n">
+      <c r="R25" s="8" t="n">
         <v>24.3</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>22.9</v>
+        <v>25.9</v>
       </c>
       <c r="T25" s="3" t="n">
         <v>56.9</v>
@@ -2624,20 +2606,20 @@
       <c r="U25" s="3" t="n">
         <v>19.7</v>
       </c>
-      <c r="V25" s="10" t="n">
+      <c r="V25" s="8" t="n">
         <v>24.2</v>
       </c>
-      <c r="W25" s="10" t="n">
+      <c r="W25" s="8" t="n">
         <v>20.9</v>
       </c>
-      <c r="X25" s="15" t="n">
+      <c r="X25" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>174.8</v>
+        <v>74.8</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>17.2</v>
+        <v>7.2</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2655,20 +2637,20 @@
       <c r="C26" s="3" t="n">
         <v>329.8</v>
       </c>
-      <c r="D26" s="10" t="n">
+      <c r="D26" s="8" t="n">
         <v>30.8</v>
       </c>
-      <c r="E26" s="10" t="n">
+      <c r="E26" s="8" t="n">
         <v>18.6</v>
       </c>
-      <c r="F26" s="10" t="n">
+      <c r="F26" s="8" t="n">
         <v>24.7</v>
       </c>
-      <c r="G26" s="10" t="n">
+      <c r="G26" s="8" t="n">
         <v>12.2</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>1.9</v>
@@ -2679,10 +2661,10 @@
       <c r="K26" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="L26" s="10" t="n">
+      <c r="L26" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="M26" s="10" t="n">
+      <c r="M26" s="8" t="n">
         <v>17.6</v>
       </c>
       <c r="N26" s="3" t="n">
@@ -2694,10 +2676,10 @@
       <c r="P26" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q26" s="10" t="n">
+      <c r="Q26" s="8" t="n">
         <v>24.4</v>
       </c>
-      <c r="R26" s="10" t="n">
+      <c r="R26" s="8" t="n">
         <v>21.8</v>
       </c>
       <c r="S26" s="3" t="n">
@@ -2707,22 +2689,22 @@
         <v>80</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="V26" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="V26" s="8" t="n">
         <v>24.2</v>
       </c>
-      <c r="W26" s="10" t="n">
+      <c r="W26" s="8" t="n">
         <v>21.8</v>
       </c>
-      <c r="X26" s="15" t="n">
+      <c r="X26" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="Y26" s="3" t="n">
         <v>81.09999999999999</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>17.6</v>
+        <v>7.6</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2738,25 +2720,25 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>1354.4</v>
-      </c>
-      <c r="D27" s="10" t="n">
+        <v>354.8</v>
+      </c>
+      <c r="D27" s="8" t="n">
         <v>28.2</v>
       </c>
-      <c r="E27" s="10" t="n">
+      <c r="E27" s="8" t="n">
         <v>19.4</v>
       </c>
-      <c r="F27" s="10" t="n">
+      <c r="F27" s="8" t="n">
         <v>23.8</v>
       </c>
-      <c r="G27" s="3" t="n">
-        <v>18.8</v>
+      <c r="G27" s="8" t="n">
+        <v>8.800000000000001</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>11.7</v>
+        <v>1.7</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>2.9</v>
@@ -2764,25 +2746,25 @@
       <c r="K27" s="3" t="n">
         <v>5.3</v>
       </c>
-      <c r="L27" s="10" t="n">
+      <c r="L27" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="M27" s="10" t="n">
+      <c r="M27" s="8" t="n">
         <v>18.8</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>20.8</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>88.5</v>
+        <v>87.5</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="Q27" s="10" t="n">
+      <c r="Q27" s="8" t="n">
         <v>26</v>
       </c>
-      <c r="R27" s="10" t="n">
+      <c r="R27" s="8" t="n">
         <v>21.6</v>
       </c>
       <c r="S27" s="3" t="n">
@@ -2791,13 +2773,13 @@
       <c r="T27" s="3" t="n">
         <v>68.40000000000001</v>
       </c>
-      <c r="U27" s="15" t="n">
+      <c r="U27" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="V27" s="10" t="n">
+      <c r="V27" s="8" t="n">
         <v>23.2</v>
       </c>
-      <c r="W27" s="10" t="n">
+      <c r="W27" s="8" t="n">
         <v>20.8</v>
       </c>
       <c r="X27" s="3" t="n">
@@ -2825,16 +2807,16 @@
       <c r="C28" s="3" t="n">
         <v>389.3</v>
       </c>
-      <c r="D28" s="10" t="n">
+      <c r="D28" s="8" t="n">
         <v>29.8</v>
       </c>
-      <c r="E28" s="10" t="n">
+      <c r="E28" s="8" t="n">
         <v>20.2</v>
       </c>
-      <c r="F28" s="10" t="n">
+      <c r="F28" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="G28" s="10" t="n">
+      <c r="G28" s="8" t="n">
         <v>9.6</v>
       </c>
       <c r="H28" s="3" t="n">
@@ -2849,10 +2831,10 @@
       <c r="K28" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="L28" s="10" t="n">
+      <c r="L28" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="M28" s="10" t="n">
+      <c r="M28" s="8" t="n">
         <v>19.2</v>
       </c>
       <c r="N28" s="3" t="n">
@@ -2864,10 +2846,10 @@
       <c r="P28" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="Q28" s="10" t="n">
+      <c r="Q28" s="8" t="n">
         <v>28.2</v>
       </c>
-      <c r="R28" s="10" t="n">
+      <c r="R28" s="8" t="n">
         <v>23</v>
       </c>
       <c r="S28" s="3" t="n">
@@ -2879,10 +2861,10 @@
       <c r="U28" s="3" t="n">
         <v>13.4</v>
       </c>
-      <c r="V28" s="10" t="n">
+      <c r="V28" s="8" t="n">
         <v>26</v>
       </c>
-      <c r="W28" s="10" t="n">
+      <c r="W28" s="8" t="n">
         <v>23.6</v>
       </c>
       <c r="X28" s="3" t="n">
@@ -2908,19 +2890,19 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="D29" s="10" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="E29" s="10" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="F29" s="10" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="D29" s="8" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="E29" s="8" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="F29" s="8" t="n">
         <v>24.9</v>
       </c>
-      <c r="G29" s="3" t="n">
-        <v>19.1</v>
+      <c r="G29" s="8" t="n">
+        <v>9.1</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>20.1</v>
@@ -2932,15 +2914,15 @@
         <v>2.9</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="L29" s="10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L29" s="3" t="n">
         <v>20.3</v>
       </c>
-      <c r="M29" s="10" t="n">
+      <c r="M29" s="8" t="n">
         <v>19.2</v>
       </c>
-      <c r="N29" s="15" t="n">
+      <c r="N29" s="3" t="n">
         <v>21.5</v>
       </c>
       <c r="O29" s="3" t="n">
@@ -2949,10 +2931,10 @@
       <c r="P29" s="3" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q29" s="10" t="n">
+      <c r="Q29" s="8" t="n">
         <v>28.6</v>
       </c>
-      <c r="R29" s="10" t="n">
+      <c r="R29" s="8" t="n">
         <v>23</v>
       </c>
       <c r="S29" s="3" t="n">
@@ -2964,10 +2946,10 @@
       <c r="U29" s="3" t="n">
         <v>14.6</v>
       </c>
-      <c r="V29" s="10" t="n">
+      <c r="V29" s="8" t="n">
         <v>25.5</v>
       </c>
-      <c r="W29" s="10" t="n">
+      <c r="W29" s="8" t="n">
         <v>23</v>
       </c>
       <c r="X29" s="3" t="n">
@@ -2995,20 +2977,20 @@
       <c r="C30" s="3" t="n">
         <v>1856.4</v>
       </c>
-      <c r="D30" s="9" t="n">
+      <c r="D30" s="8" t="n">
         <v>150.3</v>
       </c>
-      <c r="E30" s="9" t="n">
-        <v>91.2</v>
-      </c>
-      <c r="F30" s="10" t="n">
+      <c r="E30" s="8" t="n">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="F30" s="8" t="n">
         <v>124.1</v>
       </c>
-      <c r="G30" s="17" t="n">
-        <v>15.2</v>
+      <c r="G30" s="8" t="n">
+        <v>52.5</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>191.7</v>
+        <v>91.3</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>10</v>
@@ -3016,13 +2998,13 @@
       <c r="J30" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="K30" s="9" t="n">
+      <c r="K30" s="13" t="n">
         <v>25.4</v>
       </c>
-      <c r="L30" s="10" t="n">
-        <v>99.59999999999999</v>
-      </c>
-      <c r="M30" s="10" t="n">
+      <c r="L30" s="13" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="M30" s="8" t="n">
         <v>93.2</v>
       </c>
       <c r="N30" s="3" t="n">
@@ -3034,10 +3016,10 @@
       <c r="P30" s="3" t="n">
         <v>13.1</v>
       </c>
-      <c r="Q30" s="10" t="n">
+      <c r="Q30" s="8" t="n">
         <v>138.5</v>
       </c>
-      <c r="R30" s="10" t="n">
+      <c r="R30" s="8" t="n">
         <v>113.7</v>
       </c>
       <c r="S30" s="3" t="n">
@@ -3047,12 +3029,12 @@
         <v>332.8</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="V30" s="10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="V30" s="8" t="n">
         <v>123.1</v>
       </c>
-      <c r="W30" s="10" t="n">
+      <c r="W30" s="8" t="n">
         <v>110.1</v>
       </c>
       <c r="X30" s="3" t="n">
@@ -3080,34 +3062,34 @@
       <c r="C31" s="3" t="n">
         <v>37.1</v>
       </c>
-      <c r="D31" s="10" t="n">
-        <v>30</v>
-      </c>
-      <c r="E31" s="10" t="n">
+      <c r="D31" s="8" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="E31" s="8" t="n">
         <v>19.6</v>
       </c>
-      <c r="F31" s="10" t="n">
+      <c r="F31" s="8" t="n">
         <v>24.8</v>
       </c>
-      <c r="G31" s="10" t="n">
+      <c r="G31" s="8" t="n">
         <v>10.5</v>
       </c>
-      <c r="H31" s="15" t="n">
+      <c r="H31" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>13.2</v>
+        <v>3.2</v>
       </c>
       <c r="K31" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L31" s="10" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="M31" s="10" t="n">
+      <c r="L31" s="13" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="M31" s="8" t="n">
         <v>18.6</v>
       </c>
       <c r="N31" s="3" t="n">
@@ -3119,25 +3101,25 @@
       <c r="P31" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q31" s="10" t="n">
+      <c r="Q31" s="8" t="n">
         <v>27.7</v>
       </c>
-      <c r="R31" s="10" t="n">
+      <c r="R31" s="8" t="n">
         <v>22.7</v>
       </c>
-      <c r="S31" s="15" t="n">
+      <c r="S31" s="3" t="n">
         <v>24.5</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>66</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="U31" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="V31" s="10" t="n">
+      <c r="V31" s="8" t="n">
         <v>24.6</v>
       </c>
-      <c r="W31" s="10" t="n">
+      <c r="W31" s="8" t="n">
         <v>22</v>
       </c>
       <c r="X31" s="3" t="n">
@@ -3163,39 +3145,39 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>45.7</v>
-      </c>
-      <c r="D32" s="10" t="n">
-        <v>35.28</v>
-      </c>
-      <c r="E32" s="10" t="n">
+        <v>43.7</v>
+      </c>
+      <c r="D32" s="8" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="E32" s="8" t="n">
         <v>20.2</v>
       </c>
-      <c r="F32" s="10" t="n">
-        <v>27.7</v>
-      </c>
-      <c r="G32" s="15" t="n">
+      <c r="F32" s="8" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="G32" s="8" t="n">
         <v>12.6</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="J32" s="3" t="n">
         <v>4.4</v>
       </c>
-      <c r="K32" s="3" t="n">
+      <c r="K32" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L32" s="10" t="n">
+      <c r="L32" s="8" t="n">
         <v>20.6</v>
       </c>
-      <c r="M32" s="10" t="n">
+      <c r="M32" s="8" t="n">
         <v>19.3</v>
       </c>
-      <c r="N32" s="15" t="n">
+      <c r="N32" s="3" t="n">
         <v>21.5</v>
       </c>
       <c r="O32" s="3" t="n">
@@ -3204,10 +3186,10 @@
       <c r="P32" s="3" t="n">
         <v>4.8</v>
       </c>
-      <c r="Q32" s="10" t="n">
+      <c r="Q32" s="8" t="n">
         <v>31</v>
       </c>
-      <c r="R32" s="10" t="n">
+      <c r="R32" s="8" t="n">
         <v>24</v>
       </c>
       <c r="S32" s="3" t="n">
@@ -3219,17 +3201,17 @@
       <c r="U32" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="V32" s="10" t="n">
+      <c r="V32" s="8" t="n">
         <v>28.2</v>
       </c>
-      <c r="W32" s="10" t="n">
+      <c r="W32" s="8" t="n">
         <v>23.7</v>
       </c>
       <c r="X32" s="3" t="n">
         <v>26.4</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>69.09999999999999</v>
+        <v>6.9</v>
       </c>
       <c r="Z32" s="3" t="n">
         <v>11.8</v>
@@ -3248,18 +3230,18 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>397.9</v>
-      </c>
-      <c r="D33" s="10" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="E33" s="10" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="F33" s="10" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="G33" s="10" t="n">
+        <v>397</v>
+      </c>
+      <c r="D33" s="8" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="E33" s="8" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="F33" s="8" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="G33" s="8" t="n">
         <v>13.9</v>
       </c>
       <c r="H33" s="3" t="n">
@@ -3271,13 +3253,13 @@
       <c r="J33" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="K33" s="3" t="n">
+      <c r="K33" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L33" s="10" t="n">
+      <c r="L33" s="8" t="n">
         <v>20.9</v>
       </c>
-      <c r="M33" s="10" t="n">
+      <c r="M33" s="8" t="n">
         <v>19.5</v>
       </c>
       <c r="N33" s="3" t="n">
@@ -3289,25 +3271,25 @@
       <c r="P33" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="Q33" s="10" t="n">
+      <c r="Q33" s="8" t="n">
         <v>32.9</v>
       </c>
-      <c r="R33" s="10" t="n">
+      <c r="R33" s="8" t="n">
         <v>23.9</v>
       </c>
       <c r="S33" s="3" t="n">
         <v>23.9</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>147.7</v>
+        <v>47.7</v>
       </c>
       <c r="U33" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="V33" s="10" t="n">
+      <c r="V33" s="8" t="n">
         <v>25.8</v>
       </c>
-      <c r="W33" s="10" t="n">
+      <c r="W33" s="8" t="n">
         <v>22.8</v>
       </c>
       <c r="X33" s="3" t="n">
@@ -3317,7 +3299,7 @@
         <v>77.59999999999999</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>17.4</v>
+        <v>7.4</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3333,22 +3315,22 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>1362.4</v>
-      </c>
-      <c r="D34" s="10" t="n">
+        <v>362.4</v>
+      </c>
+      <c r="D34" s="8" t="n">
         <v>30.4</v>
       </c>
-      <c r="E34" s="10" t="n">
+      <c r="E34" s="8" t="n">
         <v>20.2</v>
       </c>
-      <c r="F34" s="10" t="n">
+      <c r="F34" s="8" t="n">
         <v>25.3</v>
       </c>
-      <c r="G34" s="10" t="n">
+      <c r="G34" s="8" t="n">
         <v>10.2</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>1.8</v>
+        <v>18.2</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>2.2</v>
@@ -3356,13 +3338,13 @@
       <c r="J34" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="K34" s="3" t="n">
+      <c r="K34" s="8" t="n">
         <v>1.2</v>
       </c>
-      <c r="L34" s="10" t="n">
+      <c r="L34" s="8" t="n">
         <v>20.4</v>
       </c>
-      <c r="M34" s="10" t="n">
+      <c r="M34" s="8" t="n">
         <v>19</v>
       </c>
       <c r="N34" s="3" t="n">
@@ -3374,10 +3356,10 @@
       <c r="P34" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="Q34" s="10" t="n">
+      <c r="Q34" s="8" t="n">
         <v>26.1</v>
       </c>
-      <c r="R34" s="10" t="n">
+      <c r="R34" s="8" t="n">
         <v>23.2</v>
       </c>
       <c r="S34" s="3" t="n">
@@ -3389,17 +3371,17 @@
       <c r="U34" s="3" t="n">
         <v>7.2</v>
       </c>
-      <c r="V34" s="10" t="n">
+      <c r="V34" s="8" t="n">
         <v>25.5</v>
       </c>
-      <c r="W34" s="10" t="n">
+      <c r="W34" s="8" t="n">
         <v>23.3</v>
       </c>
       <c r="X34" s="3" t="n">
         <v>27.2</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>83.2</v>
       </c>
       <c r="Z34" s="3" t="n">
         <v>5.4</v>
@@ -3420,16 +3402,16 @@
       <c r="C35" s="3" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="D35" s="10" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="E35" s="10" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="F35" s="10" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="G35" s="10" t="n">
+      <c r="D35" s="8" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="E35" s="8" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="F35" s="8" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="G35" s="8" t="n">
         <v>3.9</v>
       </c>
       <c r="H35" s="3" t="n">
@@ -3441,17 +3423,17 @@
       <c r="J35" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="K35" s="3" t="n">
+      <c r="K35" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="L35" s="10" t="n">
-        <v>20</v>
-      </c>
-      <c r="M35" s="10" t="n">
+      <c r="L35" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="M35" s="8" t="n">
         <v>19.3</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>20</v>
+        <v>21.5</v>
       </c>
       <c r="O35" s="3" t="n">
         <v>85.40000000000001</v>
@@ -3459,10 +3441,10 @@
       <c r="P35" s="3" t="n">
         <v>3.6</v>
       </c>
-      <c r="Q35" s="10" t="n">
+      <c r="Q35" s="8" t="n">
         <v>22.6</v>
       </c>
-      <c r="R35" s="10" t="n">
+      <c r="R35" s="8" t="n">
         <v>21.2</v>
       </c>
       <c r="S35" s="3" t="n">
@@ -3474,10 +3456,10 @@
       <c r="U35" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="V35" s="10" t="n">
+      <c r="V35" s="8" t="n">
         <v>21.6</v>
       </c>
-      <c r="W35" s="10" t="n">
+      <c r="W35" s="8" t="n">
         <v>20.3</v>
       </c>
       <c r="X35" s="3" t="n">
@@ -3505,19 +3487,19 @@
       <c r="C36" s="3" t="n">
         <v>398.9</v>
       </c>
-      <c r="D36" s="10" t="n">
+      <c r="D36" s="8" t="n">
         <v>28.6</v>
       </c>
-      <c r="E36" s="10" t="n">
+      <c r="E36" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="F36" s="10" t="n">
+      <c r="F36" s="8" t="n">
         <v>24.3</v>
       </c>
-      <c r="G36" s="10" t="n">
+      <c r="G36" s="8" t="n">
         <v>8.6</v>
       </c>
-      <c r="H36" s="15" t="n">
+      <c r="H36" s="3" t="n">
         <v>19</v>
       </c>
       <c r="I36" s="3" t="n">
@@ -3526,13 +3508,13 @@
       <c r="J36" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="K36" s="3" t="n">
+      <c r="K36" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L36" s="10" t="n">
+      <c r="L36" s="8" t="n">
         <v>20.6</v>
       </c>
-      <c r="M36" s="10" t="n">
+      <c r="M36" s="8" t="n">
         <v>19.4</v>
       </c>
       <c r="N36" s="3" t="n">
@@ -3544,10 +3526,10 @@
       <c r="P36" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q36" s="10" t="n">
+      <c r="Q36" s="8" t="n">
         <v>27</v>
       </c>
-      <c r="R36" s="10" t="n">
+      <c r="R36" s="8" t="n">
         <v>23.1</v>
       </c>
       <c r="S36" s="3" t="n">
@@ -3559,10 +3541,10 @@
       <c r="U36" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="V36" s="10" t="n">
+      <c r="V36" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="W36" s="10" t="n">
+      <c r="W36" s="8" t="n">
         <v>22.1</v>
       </c>
       <c r="X36" s="3" t="n">
@@ -3588,19 +3570,19 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>168.3</v>
-      </c>
-      <c r="D37" s="10" t="n">
+        <v>1683.5</v>
+      </c>
+      <c r="D37" s="8" t="n">
         <v>150.1</v>
       </c>
-      <c r="E37" s="10" t="n">
+      <c r="E37" s="8" t="n">
         <v>100.9</v>
       </c>
-      <c r="F37" s="10" t="n">
+      <c r="F37" s="8" t="n">
         <v>125.5</v>
       </c>
-      <c r="G37" s="17" t="n">
-        <v>14.9</v>
+      <c r="G37" s="8" t="n">
+        <v>49.2</v>
       </c>
       <c r="H37" s="3" t="n">
         <v>92.40000000000001</v>
@@ -3611,13 +3593,13 @@
       <c r="J37" s="3" t="n">
         <v>15.7</v>
       </c>
-      <c r="K37" s="9" t="n">
-        <v>102.8</v>
-      </c>
-      <c r="L37" s="9" t="n">
+      <c r="K37" s="8" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="L37" s="8" t="n">
         <v>103.5</v>
       </c>
-      <c r="M37" s="10" t="n">
+      <c r="M37" s="8" t="n">
         <v>96.5</v>
       </c>
       <c r="N37" s="3" t="n">
@@ -3629,10 +3611,10 @@
       <c r="P37" s="3" t="n">
         <v>14.9</v>
       </c>
-      <c r="Q37" s="10" t="n">
+      <c r="Q37" s="8" t="n">
         <v>139.6</v>
       </c>
-      <c r="R37" s="10" t="n">
+      <c r="R37" s="8" t="n">
         <v>115.4</v>
       </c>
       <c r="S37" s="3" t="n">
@@ -3644,10 +3626,10 @@
       <c r="U37" s="3" t="n">
         <v>65.7</v>
       </c>
-      <c r="V37" s="10" t="n">
+      <c r="V37" s="8" t="n">
         <v>126.1</v>
       </c>
-      <c r="W37" s="10" t="n">
+      <c r="W37" s="8" t="n">
         <v>112.2</v>
       </c>
       <c r="X37" s="3" t="n">
@@ -3673,37 +3655,37 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>2326.7</v>
-      </c>
-      <c r="D38" s="10" t="n">
+        <v>336.7</v>
+      </c>
+      <c r="D38" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="E38" s="10" t="n">
+      <c r="E38" s="8" t="n">
         <v>20.2</v>
       </c>
-      <c r="F38" s="10" t="n">
+      <c r="F38" s="8" t="n">
         <v>25.1</v>
       </c>
-      <c r="G38" s="10" t="n">
+      <c r="G38" s="8" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="H38" s="3" t="n">
         <v>18.5</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>2.5</v>
+        <v>22.5</v>
       </c>
       <c r="J38" s="3" t="n">
         <v>3.1</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L38" s="10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L38" s="8" t="n">
         <v>20.7</v>
       </c>
-      <c r="M38" s="9" t="n">
-        <v>1.9</v>
+      <c r="M38" s="8" t="n">
+        <v>19.3</v>
       </c>
       <c r="N38" s="3" t="n">
         <v>21.4</v>
@@ -3714,10 +3696,10 @@
       <c r="P38" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="Q38" s="10" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="R38" s="10" t="n">
+      <c r="Q38" s="13" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="R38" s="8" t="n">
         <v>23.1</v>
       </c>
       <c r="S38" s="3" t="n">
@@ -3727,12 +3709,12 @@
         <v>68.7</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="V38" s="10" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="V38" s="8" t="n">
         <v>25.2</v>
       </c>
-      <c r="W38" s="10" t="n">
+      <c r="W38" s="8" t="n">
         <v>22.4</v>
       </c>
       <c r="X38" s="3" t="n">
@@ -3758,18 +3740,18 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>1400.8</v>
-      </c>
-      <c r="D39" s="10" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="E39" s="10" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="F39" s="10" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="G39" s="10" t="n">
+        <v>400.8</v>
+      </c>
+      <c r="D39" s="8" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="E39" s="8" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="F39" s="8" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="G39" s="8" t="n">
         <v>12.3</v>
       </c>
       <c r="H39" s="3" t="n">
@@ -3779,18 +3761,18 @@
         <v>2.5</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="K39" s="3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K39" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L39" s="10" t="n">
+      <c r="L39" s="8" t="n">
         <v>20.5</v>
       </c>
-      <c r="M39" s="10" t="n">
+      <c r="M39" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="N39" s="15" t="n">
+      <c r="N39" s="3" t="n">
         <v>22</v>
       </c>
       <c r="O39" s="3" t="n">
@@ -3799,10 +3781,10 @@
       <c r="P39" s="3" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q39" s="10" t="n">
+      <c r="Q39" s="8" t="n">
         <v>30.4</v>
       </c>
-      <c r="R39" s="10" t="n">
+      <c r="R39" s="8" t="n">
         <v>23.1</v>
       </c>
       <c r="S39" s="3" t="n">
@@ -3814,10 +3796,10 @@
       <c r="U39" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="V39" s="10" t="n">
+      <c r="V39" s="8" t="n">
         <v>26.8</v>
       </c>
-      <c r="W39" s="10" t="n">
+      <c r="W39" s="8" t="n">
         <v>23.8</v>
       </c>
       <c r="X39" s="3" t="n">
@@ -3845,20 +3827,20 @@
       <c r="C40" s="3" t="n">
         <v>74.40000000000001</v>
       </c>
-      <c r="D40" s="10" t="n">
-        <v>24</v>
-      </c>
-      <c r="E40" s="10" t="n">
+      <c r="D40" s="8" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="E40" s="8" t="n">
         <v>20.2</v>
       </c>
-      <c r="F40" s="10" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="G40" s="3" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="H40" s="15" t="n">
-        <v>129</v>
+      <c r="F40" s="8" t="n">
+        <v>22.21</v>
+      </c>
+      <c r="G40" s="8" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H40" s="3" t="n">
+        <v>19</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>0.4</v>
@@ -3866,13 +3848,13 @@
       <c r="J40" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="K40" s="3" t="n">
+      <c r="K40" s="8" t="n">
         <v>4.9</v>
       </c>
-      <c r="L40" s="10" t="n">
+      <c r="L40" s="8" t="n">
         <v>20.4</v>
       </c>
-      <c r="M40" s="10" t="n">
+      <c r="M40" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="N40" s="3" t="n">
@@ -3884,10 +3866,10 @@
       <c r="P40" s="3" t="n">
         <v>2.7</v>
       </c>
-      <c r="Q40" s="10" t="n">
+      <c r="Q40" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="R40" s="10" t="n">
+      <c r="R40" s="8" t="n">
         <v>19.8</v>
       </c>
       <c r="S40" s="3" t="n">
@@ -3899,10 +3881,10 @@
       <c r="U40" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="V40" s="10" t="n">
+      <c r="V40" s="8" t="n">
         <v>21.3</v>
       </c>
-      <c r="W40" s="10" t="n">
+      <c r="W40" s="8" t="n">
         <v>19.6</v>
       </c>
       <c r="X40" s="3" t="n">
@@ -3928,19 +3910,19 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>244.8</v>
-      </c>
-      <c r="D41" s="3" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="E41" s="17" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="F41" s="10" t="n">
+        <v>448.2</v>
+      </c>
+      <c r="D41" s="8" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="E41" s="8" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="F41" s="8" t="n">
         <v>24.5</v>
       </c>
-      <c r="G41" s="3" t="n">
-        <v>19.9</v>
+      <c r="G41" s="8" t="n">
+        <v>9.9</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>17.4</v>
@@ -3951,13 +3933,13 @@
       <c r="J41" s="3" t="n">
         <v>3.8</v>
       </c>
-      <c r="K41" s="3" t="n">
+      <c r="K41" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L41" s="10" t="n">
+      <c r="L41" s="8" t="n">
         <v>19.9</v>
       </c>
-      <c r="M41" s="10" t="n">
+      <c r="M41" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="N41" s="3" t="n">
@@ -3969,25 +3951,25 @@
       <c r="P41" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q41" s="10" t="n">
+      <c r="Q41" s="8" t="n">
         <v>28</v>
       </c>
-      <c r="R41" s="10" t="n">
+      <c r="R41" s="8" t="n">
         <v>21.6</v>
       </c>
       <c r="S41" s="3" t="n">
         <v>21.7</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>58.4</v>
+        <v>57.4</v>
       </c>
       <c r="U41" s="3" t="n">
         <v>16.1</v>
       </c>
-      <c r="V41" s="10" t="n">
+      <c r="V41" s="8" t="n">
         <v>24.6</v>
       </c>
-      <c r="W41" s="10" t="n">
+      <c r="W41" s="8" t="n">
         <v>22.2</v>
       </c>
       <c r="X41" s="3" t="n">
@@ -4013,18 +3995,18 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>116.4</v>
-      </c>
-      <c r="D42" s="10" t="n">
+        <v>464.2</v>
+      </c>
+      <c r="D42" s="8" t="n">
         <v>32.8</v>
       </c>
-      <c r="E42" s="10" t="n">
+      <c r="E42" s="8" t="n">
         <v>17</v>
       </c>
-      <c r="F42" s="10" t="n">
+      <c r="F42" s="8" t="n">
         <v>24.9</v>
       </c>
-      <c r="G42" s="15" t="n">
+      <c r="G42" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="H42" s="3" t="n">
@@ -4036,13 +4018,13 @@
       <c r="J42" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="K42" s="3" t="n">
+      <c r="K42" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="L42" s="10" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="M42" s="10" t="n">
+      <c r="L42" s="8" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="M42" s="3" t="n">
         <v>16.1</v>
       </c>
       <c r="N42" s="3" t="n">
@@ -4054,25 +4036,25 @@
       <c r="P42" s="3" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q42" s="10" t="n">
+      <c r="Q42" s="8" t="n">
         <v>30.8</v>
       </c>
-      <c r="R42" s="10" t="n">
+      <c r="R42" s="8" t="n">
         <v>22.6</v>
       </c>
       <c r="S42" s="3" t="n">
         <v>22.2</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="U42" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="V42" s="10" t="n">
+      <c r="V42" s="8" t="n">
         <v>27.5</v>
       </c>
-      <c r="W42" s="10" t="n">
+      <c r="W42" s="8" t="n">
         <v>23.8</v>
       </c>
       <c r="X42" s="3" t="n">
@@ -4098,18 +4080,18 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>2341.3</v>
-      </c>
-      <c r="D43" s="10" t="n">
+        <v>341.3</v>
+      </c>
+      <c r="D43" s="8" t="n">
         <v>32</v>
       </c>
-      <c r="E43" s="10" t="n">
+      <c r="E43" s="8" t="n">
         <v>18.6</v>
       </c>
-      <c r="F43" s="10" t="n">
+      <c r="F43" s="8" t="n">
         <v>25.3</v>
       </c>
-      <c r="G43" s="10" t="n">
+      <c r="G43" s="8" t="n">
         <v>13.4</v>
       </c>
       <c r="H43" s="3" t="n">
@@ -4121,31 +4103,31 @@
       <c r="J43" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="K43" s="3" t="n">
+      <c r="K43" s="8" t="n">
         <v>15.2</v>
       </c>
-      <c r="L43" s="10" t="n">
+      <c r="L43" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="M43" s="10" t="n">
+      <c r="M43" s="3" t="n">
         <v>17.7</v>
       </c>
-      <c r="N43" s="15" t="n">
+      <c r="N43" s="3" t="n">
         <v>19.4</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>188.1</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Q43" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q43" s="8" t="n">
         <v>24.7</v>
       </c>
-      <c r="R43" s="10" t="n">
+      <c r="R43" s="8" t="n">
         <v>22.3</v>
       </c>
-      <c r="S43" s="15" t="n">
+      <c r="S43" s="3" t="n">
         <v>25.4</v>
       </c>
       <c r="T43" s="3" t="n">
@@ -4154,10 +4136,10 @@
       <c r="U43" s="3" t="n">
         <v>5.7</v>
       </c>
-      <c r="V43" s="10" t="n">
+      <c r="V43" s="8" t="n">
         <v>23</v>
       </c>
-      <c r="W43" s="10" t="n">
+      <c r="W43" s="8" t="n">
         <v>22.4</v>
       </c>
       <c r="X43" s="3" t="n">
@@ -4167,7 +4149,7 @@
         <v>82.8</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>14.6</v>
+        <v>4.6</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4185,16 +4167,16 @@
       <c r="C44" s="3" t="n">
         <v>141.6</v>
       </c>
-      <c r="D44" s="10" t="n">
+      <c r="D44" s="8" t="n">
         <v>23.9</v>
       </c>
-      <c r="E44" s="10" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="F44" s="10" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="G44" s="10" t="n">
+      <c r="E44" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="F44" s="8" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="G44" s="8" t="n">
         <v>4.9</v>
       </c>
       <c r="H44" s="3" t="n">
@@ -4206,17 +4188,17 @@
       <c r="J44" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="K44" s="3" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="L44" s="10" t="n">
+      <c r="K44" s="8" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="L44" s="8" t="n">
         <v>19.4</v>
       </c>
-      <c r="M44" s="10" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="N44" s="15" t="n">
-        <v>4.1</v>
+      <c r="M44" s="3" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="N44" s="3" t="n">
+        <v>20.1</v>
       </c>
       <c r="O44" s="3" t="n">
         <v>240.1</v>
@@ -4224,10 +4206,10 @@
       <c r="P44" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q44" s="10" t="n">
+      <c r="Q44" s="8" t="n">
         <v>22.6</v>
       </c>
-      <c r="R44" s="10" t="n">
+      <c r="R44" s="8" t="n">
         <v>20.3</v>
       </c>
       <c r="S44" s="3" t="n">
@@ -4237,12 +4219,12 @@
         <v>81</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="V44" s="10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="V44" s="8" t="n">
         <v>22.3</v>
       </c>
-      <c r="W44" s="10" t="n">
+      <c r="W44" s="8" t="n">
         <v>20.2</v>
       </c>
       <c r="X44" s="3" t="inlineStr"/>
@@ -4264,16 +4246,16 @@
       <c r="C45" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="D45" s="10" t="n">
+      <c r="D45" s="8" t="n">
         <v>174</v>
       </c>
-      <c r="E45" s="9" t="n">
+      <c r="E45" s="8" t="n">
         <v>113.8</v>
       </c>
-      <c r="F45" s="10" t="n">
+      <c r="F45" s="8" t="n">
         <v>144</v>
       </c>
-      <c r="G45" s="10" t="n">
+      <c r="G45" s="8" t="n">
         <v>60.2</v>
       </c>
       <c r="H45" s="3" t="n">
@@ -4285,48 +4267,48 @@
       <c r="J45" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="K45" s="9" t="n">
+      <c r="K45" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="L45" s="9" t="n">
-        <v>110.4</v>
-      </c>
-      <c r="M45" s="10" t="n">
+      <c r="L45" s="8" t="n">
+        <v>116.4</v>
+      </c>
+      <c r="M45" s="13" t="n">
         <v>109.2</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>1218.1</v>
+        <v>121.1</v>
       </c>
       <c r="O45" s="3" t="n">
         <v>534.4</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>140.4</v>
-      </c>
-      <c r="Q45" s="10" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="Q45" s="8" t="n">
         <v>157.5</v>
       </c>
-      <c r="R45" s="10" t="n">
+      <c r="R45" s="8" t="n">
         <v>129.7</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>138.5</v>
+        <v>137.5</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>424</v>
+        <v>414</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>1121.5</v>
-      </c>
-      <c r="V45" s="10" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="V45" s="8" t="n">
         <v>145.5</v>
       </c>
-      <c r="W45" s="9" t="n">
-        <v>231.2</v>
+      <c r="W45" s="13" t="n">
+        <v>131.6</v>
       </c>
       <c r="X45" s="3" t="inlineStr"/>
       <c r="Y45" s="3" t="n">
-        <v>48390.4</v>
+        <v>482</v>
       </c>
       <c r="Z45" s="3" t="n">
         <v>5.8</v>
@@ -4347,20 +4329,20 @@
       <c r="C46" s="3" t="n">
         <v>311.7</v>
       </c>
-      <c r="D46" s="10" t="n">
+      <c r="D46" s="8" t="n">
         <v>29</v>
       </c>
-      <c r="E46" s="10" t="n">
+      <c r="E46" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="F46" s="10" t="n">
+      <c r="F46" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="G46" s="15" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H46" s="15" t="n">
-        <v>167.6</v>
+      <c r="G46" s="8" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="H46" s="3" t="n">
+        <v>17.6</v>
       </c>
       <c r="I46" s="3" t="n">
         <v>2.2</v>
@@ -4368,27 +4350,29 @@
       <c r="J46" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="K46" s="3" t="inlineStr"/>
-      <c r="L46" s="10" t="n">
+      <c r="K46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" s="8" t="n">
         <v>19.4</v>
       </c>
-      <c r="M46" s="10" t="n">
+      <c r="M46" s="13" t="n">
         <v>18.2</v>
       </c>
       <c r="N46" s="3" t="n">
         <v>20.2</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>89.90000000000001</v>
+        <v>89</v>
       </c>
       <c r="P46" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q46" s="10" t="n">
+      <c r="Q46" s="8" t="n">
         <v>26.2</v>
       </c>
-      <c r="R46" s="10" t="n">
-        <v>21.6</v>
+      <c r="R46" s="13" t="n">
+        <v>221.6</v>
       </c>
       <c r="S46" s="3" t="n">
         <v>22.9</v>
@@ -4399,13 +4383,13 @@
       <c r="U46" s="3" t="n">
         <v>11.9</v>
       </c>
-      <c r="V46" s="10" t="n">
+      <c r="V46" s="8" t="n">
         <v>24.2</v>
       </c>
-      <c r="W46" s="10" t="n">
+      <c r="W46" s="8" t="n">
         <v>21.8</v>
       </c>
-      <c r="X46" s="15" t="n">
+      <c r="X46" s="3" t="n">
         <v>24.7</v>
       </c>
       <c r="Y46" s="3" t="inlineStr"/>
